--- a/data/Excel_example.xlsx
+++ b/data/Excel_example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mclainfamily/Library/CloudStorage/OneDrive-UniversityofSouthCarolina/Teaching/Summer Workshop/INBRE-Bios-Summer-26/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8937ABAF-85B5-5843-A42C-EEC3FD234F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E51202AC-95DA-AF4A-8229-0F1535A8F248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38340" windowHeight="19460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="189">
   <si>
     <t>Country</t>
   </si>
@@ -4065,10 +4065,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22FA7EC-A910-7C46-8605-70D6800CDC36}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>182</v>
       </c>
@@ -4090,8 +4093,11 @@
       <c r="G1" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>44</v>
       </c>
@@ -4113,8 +4119,11 @@
       <c r="G2">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>40</v>
       </c>
@@ -4136,8 +4145,11 @@
       <c r="G3">
         <v>185</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>44</v>
       </c>
@@ -4159,8 +4171,11 @@
       <c r="G4">
         <v>168</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>42</v>
       </c>
@@ -4182,8 +4197,11 @@
       <c r="G5">
         <v>172</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>38</v>
       </c>
@@ -4205,8 +4223,11 @@
       <c r="G6">
         <v>180</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>47</v>
       </c>
@@ -4228,8 +4249,11 @@
       <c r="G7">
         <v>176</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>40</v>
       </c>
@@ -4251,8 +4275,11 @@
       <c r="G8">
         <v>180</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>43</v>
       </c>
@@ -4274,8 +4301,11 @@
       <c r="G9">
         <v>170</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>44</v>
       </c>
@@ -4297,8 +4327,11 @@
       <c r="G10">
         <v>176</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>38</v>
       </c>
@@ -4320,8 +4353,11 @@
       <c r="G11">
         <v>186</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>44</v>
       </c>
@@ -4343,8 +4379,11 @@
       <c r="G12">
         <v>168</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>45</v>
       </c>
@@ -4366,8 +4405,11 @@
       <c r="G13">
         <v>192</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>45</v>
       </c>
@@ -4389,8 +4431,11 @@
       <c r="G14">
         <v>176</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>47</v>
       </c>
@@ -4412,8 +4457,11 @@
       <c r="G15">
         <v>164</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>54</v>
       </c>
@@ -4435,8 +4483,11 @@
       <c r="G16">
         <v>170</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>49</v>
       </c>
@@ -4458,8 +4509,11 @@
       <c r="G17">
         <v>185</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>51</v>
       </c>
@@ -4481,8 +4535,11 @@
       <c r="G18">
         <v>172</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>51</v>
       </c>
@@ -4504,8 +4561,11 @@
       <c r="G19">
         <v>168</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>48</v>
       </c>
@@ -4527,8 +4587,11 @@
       <c r="G20">
         <v>164</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>49</v>
       </c>
@@ -4550,8 +4613,11 @@
       <c r="G21">
         <v>168</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>57</v>
       </c>
@@ -4573,8 +4639,11 @@
       <c r="G22">
         <v>176</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>54</v>
       </c>
@@ -4596,8 +4665,11 @@
       <c r="G23">
         <v>165</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>52</v>
       </c>
@@ -4619,8 +4691,11 @@
       <c r="G24">
         <v>166</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>50</v>
       </c>
@@ -4642,8 +4717,11 @@
       <c r="G25">
         <v>155</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>51</v>
       </c>
@@ -4665,8 +4743,11 @@
       <c r="G26">
         <v>172</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>54</v>
       </c>
@@ -4688,8 +4769,11 @@
       <c r="G27">
         <v>172</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>51</v>
       </c>
@@ -4711,8 +4795,11 @@
       <c r="G28">
         <v>188</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>57</v>
       </c>
@@ -4734,8 +4821,11 @@
       <c r="G29">
         <v>155</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>49</v>
       </c>
@@ -4757,8 +4847,11 @@
       <c r="G30">
         <v>188</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>48</v>
       </c>
@@ -4780,8 +4873,11 @@
       <c r="G31">
         <v>176</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>52</v>
       </c>
@@ -4802,6 +4898,9 @@
       </c>
       <c r="G32">
         <v>172</v>
+      </c>
+      <c r="H32" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
